--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00867B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00867B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{038FBEF0-9765-4C61-B074-81BD7491EFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71155F63-A24D-45EB-87CB-F9A939585E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{ABBF8E51-D973-4170-9BAA-4F0BC7624327}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F42732FC-6F4F-4B5B-91F9-1A89599905B9}"/>
   </bookViews>
   <sheets>
     <sheet name="00867B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1585,25 +1585,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39038052-CC7F-41FC-B4FB-97C489C5CE81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51208044-0DD2-481B-B7B3-B6C3C129B371}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1757,7 +1757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1837,7 +1837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="49" t="s">
         <v>66</v>
       </c>
